--- a/ExcelRAddIn/Tests/Learning Excel as an R User.xlsx
+++ b/ExcelRAddIn/Tests/Learning Excel as an R User.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\Office365 AddIns\ExcelRAddIn\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFC291E-DF61-4A54-8C92-2CA81003DFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F884710-E0ED-4E11-BBF6-5DAB6AB7DC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{06B270AC-E0BE-4607-89CF-CA01D04C86B4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{06B270AC-E0BE-4607-89CF-CA01D04C86B4}"/>
   </bookViews>
   <sheets>
     <sheet name="References" sheetId="1" r:id="rId1"/>
@@ -39,8 +39,9 @@
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
+  <metadataTypes count="2">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
@@ -51,11 +52,25 @@
       </extLst>
     </bk>
   </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
 </metadata>
 </file>
 
@@ -161,12 +176,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -182,12 +203,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -212,13 +234,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>441960</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>426720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>441960</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -265,6 +287,68 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>2</v>
+    <v>8</v>
+    <v>27</v>
+    <v>1</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="colOffset" t="i"/>
+    <k n="errorType" t="i"/>
+    <k n="rwOffset" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E3631B97-09DF-43AA-8CAF-EE4BF79DCEEB}" name="Table1" displayName="Table1" ref="B2:C3" totalsRowShown="0">
   <autoFilter ref="B2:C3" xr:uid="{E3631B97-09DF-43AA-8CAF-EE4BF79DCEEB}"/>
@@ -277,9 +361,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -317,7 +401,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -423,7 +507,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -565,7 +649,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -640,7 +724,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852BAD40-8C45-4C3E-B0E9-4C9F0B70D05B}">
-  <dimension ref="B2:O53"/>
+  <dimension ref="B2:O54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="57.88671875" customWidth="1"/>
@@ -671,7 +755,7 @@
         <v>1.0000000000000002</v>
       </c>
       <c r="G3">
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0.99999999999999967</v>
@@ -689,7 +773,7 @@
         <v>1.0000000000000007</v>
       </c>
       <c r="M3">
-        <v>1.0000000000000002</v>
+        <v>0.99999999999999933</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -722,7 +806,7 @@
         <v>2688.0000000000014</v>
       </c>
       <c r="J4">
-        <v>4607.9999999999973</v>
+        <v>4607.9999999999991</v>
       </c>
       <c r="K4">
         <v>8064</v>
@@ -740,65 +824,76 @@
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D7" cm="1">
-        <f t="array" ref="D7:I7">TRANSPOSE(_xll.RScript.Evaluate(B7))</f>
+      <c r="D7" s="3" t="str" cm="1">
+        <f t="array" ref="D7:I8">TRANSPOSE(_xll.RScript.Evaluate(B7, "nv"))</f>
+        <v>Min.</v>
+      </c>
+      <c r="E7" s="3" t="str">
+        <v>1st Qu.</v>
+      </c>
+      <c r="F7" s="3" t="str">
+        <v>Median</v>
+      </c>
+      <c r="G7" s="3" t="str">
+        <v>Mean</v>
+      </c>
+      <c r="H7" s="3" t="str">
+        <v>3rd Qu.</v>
+      </c>
+      <c r="I7" s="3" t="str">
+        <v>Max.</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D8" s="3">
         <v>-2.2204460492503131E-16</v>
       </c>
-      <c r="E7">
-        <v>-2.2204460492503131E-16</v>
-      </c>
-      <c r="F7">
+      <c r="E8" s="3">
         <v>0</v>
       </c>
-      <c r="G7">
-        <v>-7.4014868308343765E-17</v>
-      </c>
-      <c r="H7">
+      <c r="F8" s="3">
         <v>0</v>
       </c>
-      <c r="I7">
+      <c r="G8" s="3">
+        <v>-1.8503717077085941E-17</v>
+      </c>
+      <c r="H8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" t="str" cm="1">
-        <f t="array" ref="D9">_xll.RScript.Evaluate(B9)</f>
-        <v>x</v>
+      <c r="I8" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" t="str" cm="1">
         <f t="array" ref="D10">_xll.RScript.Evaluate(B10)</f>
-        <v>size</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
-        <v>11</v>
+        <v>x</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>10</v>
       </c>
       <c r="D11" t="str" cm="1">
         <f t="array" ref="D11">_xll.RScript.Evaluate(B11)</f>
-        <v>Exception: Value cannot be null.</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>12</v>
+        <v>size</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="D12" t="str" cm="1">
         <f t="array" ref="D12">_xll.RScript.Evaluate(B12)</f>
-        <v>OK</v>
+        <v>Exception: Value cannot be null.</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" t="str" cm="1">
         <f t="array" ref="D13">_xll.RScript.Evaluate(B13)</f>
@@ -807,394 +902,155 @@
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" t="str" cm="1">
         <f t="array" ref="D14">_xll.RScript.Evaluate(B14)</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="str" cm="1">
+        <f t="array" ref="D15">_xll.RScript.Evaluate(B15)</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
         <v>16</v>
-      </c>
-      <c r="D17" t="str" cm="1">
-        <f t="array" ref="D17">_xll.RScript.Evaluate(B17)</f>
-        <v>x1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
-        <v>17</v>
       </c>
       <c r="D18" t="str" cm="1">
         <f t="array" ref="D18">_xll.RScript.Evaluate(B18)</f>
-        <v>x2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+        <v>x1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" t="str" cm="1">
         <f t="array" ref="D19">_xll.RScript.Evaluate(B19)</f>
-        <v>x3</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+        <v>x2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D20" t="str" cm="1">
         <f t="array" ref="D20">_xll.RScript.Evaluate(B20)</f>
-        <v>h1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+        <v>x3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D21" t="str" cm="1">
         <f t="array" ref="D21">_xll.RScript.Evaluate(B21)</f>
-        <v>h2</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+        <v>h1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D22" t="str" cm="1">
         <f t="array" ref="D22">_xll.RScript.Evaluate(B22)</f>
+        <v>h2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" t="str" cm="1">
+        <f t="array" ref="D23">_xll.RScript.Evaluate(B23)</f>
         <v>h3</v>
       </c>
     </row>
-    <row r="23" spans="2:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+    <row r="24" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D23" cm="1">
-        <f t="array" ref="D23:F45">TRANSPOSE(_xll.RScript.Evaluate(B23))</f>
-        <v>1.5</v>
-      </c>
-      <c r="E23">
-        <v>2.5</v>
-      </c>
-      <c r="F23">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D24">
-        <v>5.5</v>
-      </c>
-      <c r="E24">
-        <v>6.5</v>
-      </c>
-      <c r="F24">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D25">
-        <v>9.5</v>
-      </c>
-      <c r="E25">
-        <v>10.5</v>
-      </c>
-      <c r="F25">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D26">
-        <v>13.5</v>
-      </c>
-      <c r="E26">
-        <v>14.5</v>
-      </c>
-      <c r="F26">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D27">
-        <v>17.5</v>
-      </c>
-      <c r="E27">
-        <v>18.5</v>
-      </c>
-      <c r="F27">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D28">
-        <v>21.5</v>
-      </c>
-      <c r="E28">
-        <v>22.5</v>
-      </c>
-      <c r="F28">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D29">
-        <v>25.5</v>
-      </c>
-      <c r="E29">
-        <v>26.5</v>
-      </c>
-      <c r="F29">
-        <v>27.5</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D30">
-        <v>29.5</v>
-      </c>
-      <c r="E30">
-        <v>30.5</v>
-      </c>
-      <c r="F30">
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D31">
-        <v>33.5</v>
-      </c>
-      <c r="E31">
-        <v>34.5</v>
-      </c>
-      <c r="F31">
-        <v>35.5</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D32">
-        <v>37.5</v>
-      </c>
-      <c r="E32">
-        <v>38.5</v>
-      </c>
-      <c r="F32">
-        <v>39.5</v>
-      </c>
-    </row>
-    <row r="33" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D33">
-        <v>41.5</v>
-      </c>
-      <c r="E33">
-        <v>42.5</v>
-      </c>
-      <c r="F33">
-        <v>43.5</v>
-      </c>
-    </row>
-    <row r="34" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D34">
-        <v>45.5</v>
-      </c>
-      <c r="E34">
-        <v>46.5</v>
-      </c>
-      <c r="F34">
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="35" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D35">
-        <v>49.5</v>
-      </c>
-      <c r="E35">
-        <v>50.5</v>
-      </c>
-      <c r="F35">
-        <v>51.5</v>
-      </c>
-    </row>
-    <row r="36" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D36">
-        <v>53.5</v>
-      </c>
-      <c r="E36">
-        <v>54.5</v>
-      </c>
-      <c r="F36">
-        <v>55.5</v>
-      </c>
-    </row>
-    <row r="37" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D37">
-        <v>57.5</v>
-      </c>
-      <c r="E37">
-        <v>58.5</v>
-      </c>
-      <c r="F37">
-        <v>59.5</v>
-      </c>
-    </row>
-    <row r="38" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D38">
-        <v>61.5</v>
-      </c>
-      <c r="E38">
-        <v>62.5</v>
-      </c>
-      <c r="F38">
-        <v>63.5</v>
-      </c>
-    </row>
-    <row r="39" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D39">
-        <v>65.5</v>
-      </c>
-      <c r="E39">
-        <v>66.5</v>
-      </c>
-      <c r="F39">
-        <v>67.5</v>
-      </c>
-    </row>
-    <row r="40" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D40">
-        <v>69.5</v>
-      </c>
-      <c r="E40">
-        <v>70.5</v>
-      </c>
-      <c r="F40">
-        <v>71.5</v>
-      </c>
-    </row>
-    <row r="41" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D41">
-        <v>73.5</v>
-      </c>
-      <c r="E41">
-        <v>74.5</v>
-      </c>
-      <c r="F41">
-        <v>75.5</v>
-      </c>
-    </row>
-    <row r="42" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D42">
-        <v>77.5</v>
-      </c>
-      <c r="E42">
-        <v>78.5</v>
-      </c>
-      <c r="F42">
-        <v>79.5</v>
-      </c>
-    </row>
-    <row r="43" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D43">
-        <v>81.5</v>
-      </c>
-      <c r="E43">
-        <v>82.5</v>
-      </c>
-      <c r="F43">
-        <v>83.5</v>
-      </c>
-    </row>
-    <row r="44" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D44">
-        <v>85.5</v>
-      </c>
-      <c r="E44">
-        <v>86.5</v>
-      </c>
-      <c r="F44">
-        <v>87.5</v>
-      </c>
-    </row>
-    <row r="45" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D45">
-        <v>89.5</v>
-      </c>
-      <c r="E45">
-        <v>90.5</v>
-      </c>
-      <c r="F45">
-        <v>91.5</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" t="s">
+      <c r="D24" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="D24" ca="1">TRANSPOSE(_xll.RScript.Evaluate(B24))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
         <v>25</v>
       </c>
-      <c r="C49" t="str" cm="1">
-        <f t="array" ref="C49">_xll.RScript.Evaluate(B49)</f>
+      <c r="C50" t="str" cm="1">
+        <f t="array" ref="C50">_xll.RScript.Evaluate(B50)</f>
         <v>fitd</v>
       </c>
-      <c r="D49" t="str" cm="1">
-        <f t="array" ref="D49:D53">_xll.RScript.Evaluate(C49)</f>
+      <c r="D50" t="str" cm="1">
+        <f t="array" ref="D50:D54">_xll.RScript.Evaluate(C50)</f>
         <v>estimate</v>
       </c>
-      <c r="E49" cm="1">
-        <f t="array" ref="E49:F49">TRANSPOSE(_xll.RScript.Evaluate($C$49&amp;"$"&amp;D49))</f>
-        <v>2.6757561017392</v>
-      </c>
-      <c r="F49">
-        <v>7.5000000771447528</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="D50" t="str">
-        <v>sd</v>
-      </c>
       <c r="E50" cm="1">
-        <f t="array" ref="E50:F50">TRANSPOSE(_xll.RScript.Evaluate($C$49&amp;"$"&amp;D50))</f>
-        <v>1.4194728051557026</v>
+        <f t="array" ref="E50:F50">TRANSPOSE(_xll.RScript.Evaluate($C$50&amp;"$"&amp;D50))</f>
+        <v>2.6757561034660249</v>
       </c>
       <c r="F50">
-        <v>1.3351520070128289</v>
+        <v>7.5000000771496635</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D51" t="str">
-        <v>vcov</v>
-      </c>
-      <c r="G51" cm="1">
-        <f t="array" ref="G51:H52">TRANSPOSE(_xll.RScript.Evaluate($C$49&amp;"$"&amp;D51))</f>
-        <v>2.0149030445765992</v>
-      </c>
-      <c r="H51">
-        <v>-6.3803689285825106E-9</v>
+        <v>sd</v>
+      </c>
+      <c r="E51" cm="1">
+        <f t="array" ref="E51:F51">TRANSPOSE(_xll.RScript.Evaluate($C$50&amp;"$"&amp;D51))</f>
+        <v>1.4194728051557026</v>
+      </c>
+      <c r="F51">
+        <v>1.3351520048988903</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D52" t="str">
-        <v>loglik</v>
-      </c>
-      <c r="E52" cm="1">
-        <f t="array" ref="E52">TRANSPOSE(_xll.RScript.Evaluate($C$49&amp;"$"&amp;D52))</f>
-        <v>-47.399830685726791</v>
-      </c>
-      <c r="G52">
-        <v>-6.3803689285825098E-9</v>
+        <v>vcov</v>
+      </c>
+      <c r="G52" cm="1">
+        <f t="array" ref="G52:H53">TRANSPOSE(_xll.RScript.Evaluate($C$50&amp;"$"&amp;D52))</f>
+        <v>2.0149030445765992</v>
       </c>
       <c r="H52">
-        <v>1.7826308818303849</v>
+        <v>-1.2760737816757015E-8</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D53" t="str">
+        <v>loglik</v>
+      </c>
+      <c r="E53" cm="1">
+        <f t="array" ref="E53">TRANSPOSE(_xll.RScript.Evaluate($C$50&amp;"$"&amp;D53))</f>
+        <v>-47.399830685726805</v>
+      </c>
+      <c r="G53">
+        <v>-1.2760737816757015E-8</v>
+      </c>
+      <c r="H53">
+        <v>1.7826308761855265</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D54" t="str">
         <v>n</v>
       </c>
-      <c r="E53" cm="1">
-        <f t="array" ref="E53">TRANSPOSE(_xll.RScript.Evaluate($C$49&amp;"$"&amp;D53))</f>
+      <c r="E54" cm="1">
+        <f t="array" ref="E54">TRANSPOSE(_xll.RScript.Evaluate($C$50&amp;"$"&amp;D54))</f>
         <v>16</v>
       </c>
     </row>
